--- a/tasks/finalpool/canvas-enrollment-overview-excel-email/groundtruth_workspace/Spring2014_Enrollment.xlsx
+++ b/tasks/finalpool/canvas-enrollment-overview-excel-email/groundtruth_workspace/Spring2014_Enrollment.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,11 +440,6 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>TA_Count</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
           <t>Student_Teacher_Ratio</t>
         </is>
       </c>
@@ -467,9 +462,6 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
         <v>694</v>
       </c>
     </row>
@@ -491,9 +483,6 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
         <v>833</v>
       </c>
     </row>
@@ -515,9 +504,6 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
         <v>409.3</v>
       </c>
     </row>
@@ -539,9 +525,6 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
         <v>750</v>
       </c>
     </row>
@@ -563,9 +546,6 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -587,9 +567,6 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
         <v>968</v>
       </c>
     </row>
